--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2359-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2359-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{763A3497-0424-472B-A8D1-9CFF8C98868B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E317013-C65C-44C3-96A2-FA23264DDA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8F55721D-8713-45BB-865B-AF555ECDD757}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C023A729-F1BE-45FD-9A4E-678CA880D603}"/>
   </bookViews>
   <sheets>
     <sheet name="2359-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1502,29 +1502,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20947465-C5FC-429C-91A7-385324817F86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2601D210-F2FD-48BB-9E23-0970842FAA89}">
   <dimension ref="A1:X56"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="6.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1558,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1714,7 +1714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2021</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2020</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2019</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2018</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2017</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2016</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2015</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2014</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2013</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2012</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2011</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2010</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2009</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2008</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2007</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2006</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2005</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2004</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2003</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2002</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2001</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>2000</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>1999</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1998</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>1997</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>1996</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>1995</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>1994</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>1993</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>1992</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>55</v>
       </c>
